--- a/data/trans_orig/IP74A5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP74A5_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los impuestos.. en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
